--- a/data/shsh_js/concentration.xlsx
+++ b/data/shsh_js/concentration.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,764 +476,1010 @@
           <t>金山省界站</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>TARGET_POLLUTANT</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45973.58333333334</v>
+        <v>46068.66666666666</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="C2" t="n">
-        <v>0.96</v>
+        <v>2.1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2</v>
+        <v>3.2</v>
       </c>
       <c r="E2" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="F2" t="n">
-        <v>5.27</v>
+        <v>4</v>
       </c>
       <c r="G2" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
+        <v>7.5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.8</v>
+      </c>
       <c r="I2" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="J2" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2.9</v>
+      </c>
       <c r="K2" t="n">
-        <v>0.01</v>
+        <v>4.6</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>硫化氢</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45973.625</v>
+        <v>46068.70833333334</v>
       </c>
       <c r="B3" t="n">
-        <v>0.03</v>
+        <v>3.9</v>
       </c>
       <c r="C3" t="n">
-        <v>1.37</v>
+        <v>2.3</v>
       </c>
       <c r="D3" t="n">
-        <v>0.25</v>
+        <v>3.1</v>
       </c>
       <c r="E3" t="n">
-        <v>0.22</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>5.51</v>
+        <v>4</v>
       </c>
       <c r="G3" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
+        <v>7.8</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.8</v>
+      </c>
       <c r="I3" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+        <v>2.2</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>硫化氢</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45973.66666666666</v>
+        <v>46068.75</v>
       </c>
       <c r="B4" t="n">
-        <v>0.11</v>
+        <v>3.5</v>
       </c>
       <c r="C4" t="n">
-        <v>0.89</v>
+        <v>1.4</v>
       </c>
       <c r="D4" t="n">
-        <v>0.34</v>
+        <v>3.2</v>
       </c>
       <c r="E4" t="n">
-        <v>0.42</v>
+        <v>1.3</v>
       </c>
       <c r="F4" t="n">
-        <v>5.62</v>
+        <v>3.3</v>
       </c>
       <c r="G4" t="n">
-        <v>4.86</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
+        <v>7.7</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.7</v>
+      </c>
       <c r="I4" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="J4" t="inlineStr"/>
+        <v>3.1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.8</v>
+      </c>
       <c r="K4" t="n">
-        <v>6.31</v>
+        <v>4.3</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>硫化氢</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45973.70833333334</v>
+        <v>46068.79166666666</v>
       </c>
       <c r="B5" t="n">
-        <v>0.14</v>
+        <v>2.8</v>
       </c>
       <c r="C5" t="n">
-        <v>0.96</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>0.35</v>
+        <v>2.9</v>
       </c>
       <c r="E5" t="n">
-        <v>0.43</v>
+        <v>1.3</v>
       </c>
       <c r="F5" t="n">
-        <v>5.68</v>
+        <v>3.5</v>
       </c>
       <c r="G5" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
+        <v>7.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.8</v>
+      </c>
       <c r="I5" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="J5" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3</v>
+      </c>
       <c r="K5" t="n">
-        <v>1.44</v>
+        <v>3.4</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>硫化氢</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45973.75</v>
+        <v>46068.83333333334</v>
       </c>
       <c r="B6" t="n">
-        <v>0.11</v>
+        <v>3.3</v>
       </c>
       <c r="C6" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>0.32</v>
+        <v>2.5</v>
       </c>
       <c r="E6" t="n">
-        <v>0.27</v>
+        <v>1.3</v>
       </c>
       <c r="F6" t="n">
-        <v>9.380000000000001</v>
+        <v>3.4</v>
       </c>
       <c r="G6" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
       <c r="I6" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="J6" t="inlineStr"/>
+        <v>2.9</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3</v>
+      </c>
       <c r="K6" t="n">
-        <v>8.16</v>
+        <v>4.1</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>硫化氢</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45973.79166666666</v>
+        <v>46068.875</v>
       </c>
       <c r="B7" t="n">
-        <v>0.21</v>
+        <v>3.2</v>
       </c>
       <c r="C7" t="n">
-        <v>2.36</v>
+        <v>2.1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.55</v>
+        <v>2.7</v>
       </c>
       <c r="E7" t="n">
-        <v>0.44</v>
+        <v>1.1</v>
       </c>
       <c r="F7" t="n">
-        <v>9.470000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="G7" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
+        <v>7.5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.7</v>
+      </c>
       <c r="I7" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="J7" t="inlineStr"/>
+        <v>2.9</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.7</v>
+      </c>
       <c r="K7" t="n">
-        <v>4.93</v>
+        <v>4.1</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>硫化氢</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45973.83333333334</v>
+        <v>46068.91666666666</v>
       </c>
       <c r="B8" t="n">
-        <v>0.37</v>
+        <v>2.6</v>
       </c>
       <c r="C8" t="n">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="E8" t="n">
-        <v>0.99</v>
+        <v>0.8</v>
       </c>
       <c r="F8" t="n">
-        <v>9.59</v>
+        <v>2.9</v>
       </c>
       <c r="G8" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="H8" t="inlineStr"/>
+        <v>7.2</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="I8" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="J8" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.7</v>
+      </c>
       <c r="K8" t="n">
-        <v>14.71</v>
+        <v>3.2</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>硫化氢</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45973.875</v>
+        <v>46068.95833333334</v>
       </c>
       <c r="B9" t="n">
-        <v>0.33</v>
+        <v>2.8</v>
       </c>
       <c r="C9" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="D9" t="n">
-        <v>0.45</v>
+        <v>2.1</v>
       </c>
       <c r="E9" t="n">
-        <v>0.77</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>9.640000000000001</v>
+        <v>2.6</v>
       </c>
       <c r="G9" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="H9" t="inlineStr"/>
+        <v>7.4</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="I9" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="J9" t="inlineStr"/>
+        <v>2.7</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.7</v>
+      </c>
       <c r="K9" t="n">
-        <v>17.5</v>
+        <v>3.7</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>硫化氢</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45973.91666666666</v>
+        <v>46069</v>
       </c>
       <c r="B10" t="n">
-        <v>0.25</v>
+        <v>3.1</v>
       </c>
       <c r="C10" t="n">
-        <v>1.21</v>
+        <v>1.9</v>
       </c>
       <c r="D10" t="n">
-        <v>0.74</v>
+        <v>2.2</v>
       </c>
       <c r="E10" t="n">
-        <v>0.53</v>
+        <v>0.7</v>
       </c>
       <c r="F10" t="n">
-        <v>9.550000000000001</v>
+        <v>3.2</v>
       </c>
       <c r="G10" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="H10" t="inlineStr"/>
+        <v>7.3</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.5</v>
+      </c>
       <c r="I10" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+        <v>2.4</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>硫化氢</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45973.95833333334</v>
+        <v>46069.04166666666</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3</v>
+        <v>3.1</v>
       </c>
       <c r="C11" t="n">
-        <v>1.21</v>
+        <v>2.1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.57</v>
+        <v>2.8</v>
       </c>
       <c r="E11" t="n">
-        <v>0.49</v>
+        <v>0.8</v>
       </c>
       <c r="F11" t="n">
-        <v>9.59</v>
+        <v>3</v>
       </c>
       <c r="G11" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="H11" t="inlineStr"/>
+        <v>7.1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.7</v>
+      </c>
       <c r="I11" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+        <v>2.6</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K11" t="n">
+        <v>146.3</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>硫化氢</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45974</v>
+        <v>46069.08333333334</v>
       </c>
       <c r="B12" t="n">
-        <v>0.44</v>
+        <v>3.3</v>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="D12" t="n">
-        <v>0.79</v>
+        <v>2.3</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="F12" t="n">
-        <v>19.56</v>
+        <v>3</v>
       </c>
       <c r="G12" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="H12" t="inlineStr"/>
+        <v>7.1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.6</v>
+      </c>
       <c r="I12" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+        <v>3.5</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="K12" t="n">
+        <v>291.1</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>硫化氢</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45974.04166666666</v>
+        <v>46069.125</v>
       </c>
       <c r="B13" t="n">
-        <v>0.62</v>
+        <v>3.2</v>
       </c>
       <c r="C13" t="n">
-        <v>1.07</v>
+        <v>2.3</v>
       </c>
       <c r="D13" t="n">
-        <v>0.71</v>
+        <v>2.4</v>
       </c>
       <c r="E13" t="n">
-        <v>0.46</v>
+        <v>0.8</v>
       </c>
       <c r="F13" t="n">
-        <v>19.81</v>
+        <v>3.1</v>
       </c>
       <c r="G13" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="H13" t="inlineStr"/>
+        <v>6.8</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.3</v>
+      </c>
       <c r="I13" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="J13" t="inlineStr"/>
+        <v>2.4</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.7</v>
+      </c>
       <c r="K13" t="n">
-        <v>0.88</v>
+        <v>297</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>硫化氢</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45974.08333333334</v>
+        <v>46069.16666666666</v>
       </c>
       <c r="B14" t="n">
-        <v>0.38</v>
+        <v>3.3</v>
       </c>
       <c r="C14" t="n">
-        <v>1.12</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>0.54</v>
+        <v>2.4</v>
       </c>
       <c r="E14" t="n">
-        <v>0.49</v>
+        <v>0.8</v>
       </c>
       <c r="F14" t="n">
-        <v>20.11</v>
+        <v>3</v>
       </c>
       <c r="G14" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="H14" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="H14" t="n">
+        <v>7.3</v>
+      </c>
       <c r="I14" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="J14" t="inlineStr"/>
+        <v>2.6</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.6</v>
+      </c>
       <c r="K14" t="n">
-        <v>0.74</v>
+        <v>298</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>硫化氢</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45974.125</v>
+        <v>46069.20833333334</v>
       </c>
       <c r="B15" t="n">
-        <v>0.35</v>
+        <v>3.4</v>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="D15" t="n">
-        <v>0.62</v>
+        <v>2.5</v>
       </c>
       <c r="E15" t="n">
-        <v>0.51</v>
+        <v>0.7</v>
       </c>
       <c r="F15" t="n">
-        <v>19.83</v>
+        <v>2.9</v>
       </c>
       <c r="G15" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="H15" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.7</v>
+      </c>
       <c r="I15" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="J15" t="inlineStr"/>
+        <v>2.7</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.6</v>
+      </c>
       <c r="K15" t="n">
-        <v>0.79</v>
+        <v>298.1</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>硫化氢</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45974.16666666666</v>
+        <v>46069.25</v>
       </c>
       <c r="B16" t="n">
-        <v>0.39</v>
+        <v>2.4</v>
       </c>
       <c r="C16" t="n">
-        <v>1.09</v>
+        <v>2.6</v>
       </c>
       <c r="D16" t="n">
-        <v>0.61</v>
+        <v>2.2</v>
       </c>
       <c r="E16" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="F16" t="n">
-        <v>40.27</v>
+        <v>2.6</v>
       </c>
       <c r="G16" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="H16" t="inlineStr"/>
+        <v>6.9</v>
+      </c>
+      <c r="H16" t="n">
+        <v>5</v>
+      </c>
       <c r="I16" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="J16" t="inlineStr"/>
+        <v>2.5</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.5</v>
+      </c>
       <c r="K16" t="n">
-        <v>0.6899999999999999</v>
+        <v>298.7</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>硫化氢</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45974.20833333334</v>
+        <v>46069.29166666666</v>
       </c>
       <c r="B17" t="n">
-        <v>0.33</v>
+        <v>2.4</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>0.62</v>
+        <v>2.3</v>
       </c>
       <c r="E17" t="n">
-        <v>0.49</v>
+        <v>0.4</v>
       </c>
       <c r="F17" t="n">
-        <v>41.12</v>
+        <v>2.7</v>
       </c>
       <c r="G17" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="H17" t="inlineStr"/>
+        <v>6.8</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.6</v>
+      </c>
       <c r="I17" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="J17" t="inlineStr"/>
+        <v>2.8</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.4</v>
+      </c>
       <c r="K17" t="n">
-        <v>0.86</v>
+        <v>296.6</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>硫化氢</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45974.25</v>
+        <v>46069.33333333334</v>
       </c>
       <c r="B18" t="n">
-        <v>0.46</v>
+        <v>2.4</v>
       </c>
       <c r="C18" t="n">
-        <v>0.76</v>
+        <v>2.3</v>
       </c>
       <c r="D18" t="n">
-        <v>0.52</v>
+        <v>1.4</v>
       </c>
       <c r="E18" t="n">
-        <v>0.49</v>
+        <v>0.3</v>
       </c>
       <c r="F18" t="n">
-        <v>41.4</v>
+        <v>2.9</v>
       </c>
       <c r="G18" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="H18" t="inlineStr"/>
+        <v>6.7</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.4</v>
+      </c>
       <c r="I18" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="J18" t="inlineStr"/>
+        <v>2.9</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.4</v>
+      </c>
       <c r="K18" t="n">
-        <v>0.63</v>
+        <v>296.1</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>硫化氢</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45974.29166666666</v>
+        <v>46069.375</v>
       </c>
       <c r="B19" t="n">
-        <v>0.29</v>
+        <v>3.1</v>
       </c>
       <c r="C19" t="n">
-        <v>0.55</v>
+        <v>2.1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.44</v>
+        <v>1.5</v>
       </c>
       <c r="E19" t="n">
-        <v>0.47</v>
+        <v>0.4</v>
       </c>
       <c r="F19" t="n">
-        <v>41.49</v>
+        <v>2.7</v>
       </c>
       <c r="G19" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="H19" t="inlineStr"/>
+        <v>6.5</v>
+      </c>
+      <c r="H19" t="n">
+        <v>6.1</v>
+      </c>
       <c r="I19" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="J19" t="inlineStr"/>
+        <v>3.8</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.3</v>
+      </c>
       <c r="K19" t="n">
-        <v>0.58</v>
+        <v>298.4</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>硫化氢</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45974.33333333334</v>
+        <v>46069.41666666666</v>
       </c>
       <c r="B20" t="n">
-        <v>0.22</v>
+        <v>2.9</v>
       </c>
       <c r="C20" t="n">
-        <v>0.53</v>
+        <v>1.9</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4</v>
+        <v>2.2</v>
       </c>
       <c r="E20" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="F20" t="n">
-        <v>62.2</v>
+        <v>2.7</v>
       </c>
       <c r="G20" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="H20" t="inlineStr"/>
+        <v>6.4</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.8</v>
+      </c>
       <c r="I20" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="J20" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.3</v>
+      </c>
       <c r="K20" t="n">
-        <v>0.49</v>
+        <v>3.1</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>硫化氢</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45974.375</v>
+        <v>46069.45833333334</v>
       </c>
       <c r="B21" t="n">
-        <v>0.17</v>
+        <v>2.8</v>
       </c>
       <c r="C21" t="n">
-        <v>0.43</v>
+        <v>2</v>
       </c>
       <c r="D21" t="n">
-        <v>0.22</v>
+        <v>2.3</v>
       </c>
       <c r="E21" t="n">
-        <v>0.16</v>
+        <v>0.6</v>
       </c>
       <c r="F21" t="n">
-        <v>62.96</v>
+        <v>2.4</v>
       </c>
       <c r="G21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="H21" t="inlineStr"/>
+        <v>6.5</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3.6</v>
+      </c>
       <c r="I21" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="J21" t="inlineStr"/>
+        <v>2.1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.3</v>
+      </c>
       <c r="K21" t="n">
-        <v>0.4</v>
+        <v>3.2</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>硫化氢</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45974.41666666666</v>
+        <v>46069.5</v>
       </c>
       <c r="B22" t="n">
-        <v>0.1</v>
+        <v>2.3</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="D22" t="n">
-        <v>0.16</v>
+        <v>1.8</v>
       </c>
       <c r="E22" t="n">
-        <v>0.16</v>
+        <v>0.4</v>
       </c>
       <c r="F22" t="n">
-        <v>62.79</v>
+        <v>2.7</v>
       </c>
       <c r="G22" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="H22" t="inlineStr"/>
+        <v>6.3</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.6</v>
+      </c>
       <c r="I22" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="J22" t="inlineStr"/>
+        <v>2.4</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2.5</v>
+      </c>
       <c r="K22" t="n">
-        <v>0.49</v>
+        <v>3.5</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>硫化氢</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45974.45833333334</v>
+        <v>46069.54166666666</v>
       </c>
       <c r="B23" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="C23" t="inlineStr"/>
+        <v>2.4</v>
+      </c>
+      <c r="C23" t="n">
+        <v>2.9</v>
+      </c>
       <c r="D23" t="n">
-        <v>0.17</v>
+        <v>1.6</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="F23" t="n">
-        <v>63.58</v>
+        <v>2.8</v>
       </c>
       <c r="G23" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="H23" t="inlineStr"/>
+        <v>6.2</v>
+      </c>
+      <c r="H23" t="n">
+        <v>3.4</v>
+      </c>
       <c r="I23" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J23" t="inlineStr"/>
+        <v>2.7</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2.5</v>
+      </c>
       <c r="K23" t="n">
-        <v>0.32</v>
+        <v>3.7</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>硫化氢</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45974.5</v>
+        <v>46069.58333333334</v>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="inlineStr"/>
+        <v>2.8</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1.8</v>
+      </c>
       <c r="D24" t="n">
-        <v>0.14</v>
+        <v>2.2</v>
       </c>
       <c r="E24" t="n">
-        <v>0.13</v>
+        <v>0.7</v>
       </c>
       <c r="F24" t="n">
-        <v>3.47</v>
+        <v>2.6</v>
       </c>
       <c r="G24" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="H24" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="H24" t="n">
+        <v>4.7</v>
+      </c>
       <c r="I24" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="J24" t="inlineStr"/>
+        <v>2.3</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2.5</v>
+      </c>
       <c r="K24" t="n">
-        <v>0.28</v>
+        <v>3.6</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>硫化氢</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45974.54166666666</v>
+        <v>46069.625</v>
       </c>
       <c r="B25" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C25" t="inlineStr"/>
+        <v>2.8</v>
+      </c>
+      <c r="C25" t="n">
+        <v>2.3</v>
+      </c>
       <c r="D25" t="n">
-        <v>0.11</v>
+        <v>2</v>
       </c>
       <c r="E25" t="n">
-        <v>0.11</v>
+        <v>2.3</v>
       </c>
       <c r="F25" t="n">
-        <v>1.34</v>
+        <v>2.3</v>
       </c>
       <c r="G25" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="H25" t="inlineStr"/>
+        <v>6.2</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.1</v>
+      </c>
       <c r="I25" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="J25" t="inlineStr"/>
+        <v>3.4</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2.5</v>
+      </c>
       <c r="K25" t="n">
-        <v>0.22</v>
+        <v>4.1</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>硫化氢</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45974.58333333334</v>
+        <v>46069.66666666666</v>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" t="inlineStr"/>
+        <v>2.5</v>
+      </c>
+      <c r="C26" t="n">
+        <v>2.7</v>
+      </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="E26" t="n">
-        <v>0.13</v>
+        <v>3.7</v>
       </c>
       <c r="F26" t="n">
-        <v>1.58</v>
+        <v>2.3</v>
       </c>
       <c r="G26" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="H26" t="inlineStr"/>
+        <v>6.2</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.9</v>
+      </c>
       <c r="I26" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="J26" t="inlineStr"/>
+        <v>2.8</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2.6</v>
+      </c>
       <c r="K26" t="n">
-        <v>0.21</v>
+        <v>2.7</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>硫化氢</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/data/shsh_js/concentration.xlsx
+++ b/data/shsh_js/concentration.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,1001 +484,521 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46068.66666666666</v>
+        <v>46126.33333333334</v>
       </c>
       <c r="B2" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="C2" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="D2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K2" t="n">
         <v>3.2</v>
       </c>
-      <c r="E2" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="F2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G2" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="I2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J2" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="K2" t="n">
-        <v>4.6</v>
-      </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>硫化氢</t>
+          <t>硫化氢(H₂S)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46068.70833333334</v>
+        <v>46126.375</v>
       </c>
       <c r="B3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E3" t="n">
         <v>3.9</v>
       </c>
-      <c r="C3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="D3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J3" t="n">
         <v>2</v>
       </c>
-      <c r="F3" t="n">
-        <v>4</v>
-      </c>
-      <c r="G3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="I3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J3" t="n">
-        <v>3</v>
-      </c>
       <c r="K3" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>硫化氢</t>
+          <t>硫化氢(H₂S)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46068.75</v>
+        <v>46126.41666666666</v>
       </c>
       <c r="B4" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="C4" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2</v>
+        <v>5.8</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3</v>
+        <v>4.8</v>
       </c>
       <c r="F4" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="G4" t="n">
-        <v>7.7</v>
+        <v>218.9</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="I4" t="n">
-        <v>3.1</v>
+        <v>5.5</v>
       </c>
       <c r="J4" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>硫化氢</t>
+          <t>硫化氢(H₂S)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46068.79166666666</v>
+        <v>46126.45833333334</v>
       </c>
       <c r="B5" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="D5" t="n">
-        <v>2.9</v>
+        <v>6.6</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3</v>
+        <v>5.9</v>
       </c>
       <c r="F5" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="G5" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>6.7</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="K5" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>硫化氢</t>
+          <t>硫化氢(H₂S)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46068.83333333334</v>
+        <v>46126.5</v>
       </c>
       <c r="B6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D6" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="E6" t="n">
         <v>3.3</v>
       </c>
-      <c r="C6" t="n">
-        <v>2</v>
-      </c>
-      <c r="D6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1.3</v>
-      </c>
       <c r="F6" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="G6" t="n">
-        <v>8</v>
+        <v>4.6</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="I6" t="n">
-        <v>2.9</v>
+        <v>8.4</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="K6" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>硫化氢</t>
+          <t>硫化氢(H₂S)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46068.875</v>
+        <v>46126.54166666666</v>
       </c>
       <c r="B7" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="C7" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="D7" t="n">
-        <v>2.7</v>
+        <v>6.3</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1</v>
+        <v>56.5</v>
       </c>
       <c r="F7" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="G7" t="n">
-        <v>7.5</v>
+        <v>3.3</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="I7" t="n">
-        <v>2.9</v>
+        <v>5</v>
       </c>
       <c r="J7" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>硫化氢</t>
+          <t>硫化氢(H₂S)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46068.91666666666</v>
+        <v>46126.58333333334</v>
       </c>
       <c r="B8" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="C8" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>2.5</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8</v>
+        <v>247</v>
       </c>
       <c r="F8" t="n">
         <v>2.9</v>
       </c>
       <c r="G8" t="n">
-        <v>7.2</v>
+        <v>3.3</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="J8" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="K8" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>硫化氢</t>
+          <t>硫化氢(H₂S)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46068.95833333334</v>
+        <v>46126.625</v>
       </c>
       <c r="B9" t="n">
-        <v>2.8</v>
+        <v>4.4</v>
       </c>
       <c r="C9" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="D9" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J9" t="n">
         <v>2.1</v>
       </c>
-      <c r="E9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="G9" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2.7</v>
-      </c>
       <c r="K9" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>硫化氢</t>
+          <t>硫化氢(H₂S)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46069</v>
+        <v>46126.66666666666</v>
       </c>
       <c r="B10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3</v>
+      </c>
+      <c r="G10" t="n">
         <v>3.1</v>
       </c>
-      <c r="C10" t="n">
+      <c r="H10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J10" t="n">
         <v>1.9</v>
       </c>
-      <c r="D10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="G10" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I10" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2.3</v>
-      </c>
       <c r="K10" t="n">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>硫化氢</t>
+          <t>硫化氢(H₂S)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46069.04166666666</v>
+        <v>46126.70833333334</v>
       </c>
       <c r="B11" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="E11" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J11" t="n">
         <v>2.1</v>
       </c>
-      <c r="D11" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F11" t="n">
-        <v>3</v>
-      </c>
-      <c r="G11" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I11" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J11" t="n">
-        <v>2.5</v>
-      </c>
       <c r="K11" t="n">
-        <v>146.3</v>
+        <v>4.3</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>硫化氢</t>
+          <t>硫化氢(H₂S)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46069.08333333334</v>
+        <v>46126.75</v>
       </c>
       <c r="B12" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="C12" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="D12" t="n">
-        <v>2.3</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>0.7</v>
+        <v>5.2</v>
       </c>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="G12" t="n">
-        <v>7.1</v>
+        <v>3.9</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="I12" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="J12" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="K12" t="n">
-        <v>291.1</v>
+        <v>4</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>硫化氢</t>
+          <t>硫化氢(H₂S)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46069.125</v>
+        <v>46126.79166666666</v>
       </c>
       <c r="B13" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="C13" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>2.4</v>
+        <v>7.5</v>
       </c>
       <c r="E13" t="n">
-        <v>0.8</v>
+        <v>3.9</v>
       </c>
       <c r="F13" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="G13" t="n">
-        <v>6.8</v>
+        <v>3.9</v>
       </c>
       <c r="H13" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="I13" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="J13" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="K13" t="n">
-        <v>297</v>
+        <v>4.1</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>硫化氢</t>
+          <t>硫化氢(H₂S)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46069.16666666666</v>
+        <v>46126.83333333334</v>
       </c>
       <c r="B14" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.4</v>
+        <v>7.1</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8</v>
+        <v>3.2</v>
       </c>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="G14" t="n">
-        <v>7</v>
+        <v>3.7</v>
       </c>
       <c r="H14" t="n">
-        <v>7.3</v>
+        <v>1.9</v>
       </c>
       <c r="I14" t="n">
-        <v>2.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="K14" t="n">
-        <v>298</v>
+        <v>4.8</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>硫化氢</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>46069.20833333334</v>
-      </c>
-      <c r="B15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="C15" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="D15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F15" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="G15" t="n">
-        <v>7</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="I15" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="K15" t="n">
-        <v>298.1</v>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>硫化氢</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="n">
-        <v>46069.25</v>
-      </c>
-      <c r="B16" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="C16" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="D16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F16" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="G16" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="H16" t="n">
-        <v>5</v>
-      </c>
-      <c r="I16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K16" t="n">
-        <v>298.7</v>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>硫化氢</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n">
-        <v>46069.29166666666</v>
-      </c>
-      <c r="B17" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="C17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F17" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="G17" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="I17" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="K17" t="n">
-        <v>296.6</v>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>硫化氢</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n">
-        <v>46069.33333333334</v>
-      </c>
-      <c r="B18" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="C18" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="D18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F18" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="G18" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="I18" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="K18" t="n">
-        <v>296.1</v>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>硫化氢</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n">
-        <v>46069.375</v>
-      </c>
-      <c r="B19" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="C19" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="D19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F19" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="G19" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="H19" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="I19" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J19" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="K19" t="n">
-        <v>298.4</v>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>硫化氢</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n">
-        <v>46069.41666666666</v>
-      </c>
-      <c r="B20" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="C20" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="D20" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F20" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="G20" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="H20" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="I20" t="n">
-        <v>3</v>
-      </c>
-      <c r="J20" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="K20" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>硫化氢</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>46069.45833333334</v>
-      </c>
-      <c r="B21" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="C21" t="n">
-        <v>2</v>
-      </c>
-      <c r="D21" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F21" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="G21" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="H21" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="I21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J21" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="K21" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>硫化氢</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="n">
-        <v>46069.5</v>
-      </c>
-      <c r="B22" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="C22" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="D22" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F22" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="G22" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="H22" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="I22" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J22" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>硫化氢</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>46069.54166666666</v>
-      </c>
-      <c r="B23" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="C23" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="D23" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F23" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="G23" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="H23" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="I23" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J23" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K23" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>硫化氢</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n">
-        <v>46069.58333333334</v>
-      </c>
-      <c r="B24" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="C24" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="D24" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F24" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="G24" t="n">
-        <v>6</v>
-      </c>
-      <c r="H24" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="I24" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K24" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>硫化氢</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="n">
-        <v>46069.625</v>
-      </c>
-      <c r="B25" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="C25" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="D25" t="n">
-        <v>2</v>
-      </c>
-      <c r="E25" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="F25" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="G25" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="H25" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="I25" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J25" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K25" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>硫化氢</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="n">
-        <v>46069.66666666666</v>
-      </c>
-      <c r="B26" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="C26" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="D26" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="E26" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="F26" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="G26" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="I26" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J26" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="K26" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>硫化氢</t>
+          <t>硫化氢(H₂S)</t>
         </is>
       </c>
     </row>

--- a/data/shsh_js/concentration.xlsx
+++ b/data/shsh_js/concentration.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,521 +484,1287 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46126.33333333334</v>
+        <v>46045.41666666666</v>
       </c>
       <c r="B2" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2.2</v>
-      </c>
+        <v>0.27</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>7.4</v>
+        <v>0.45</v>
       </c>
       <c r="E2" t="n">
-        <v>2.5</v>
+        <v>0.62</v>
       </c>
       <c r="F2" t="n">
-        <v>4.6</v>
+        <v>1.48</v>
       </c>
       <c r="G2" t="n">
-        <v>3.1</v>
+        <v>0.64</v>
       </c>
       <c r="H2" t="n">
-        <v>2.2</v>
+        <v>1.62</v>
       </c>
       <c r="I2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J2" t="n">
-        <v>2</v>
-      </c>
+        <v>0.38</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>3.2</v>
+        <v>0.46</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>硫化氢(H₂S)</t>
+          <t>苯</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46126.375</v>
+        <v>46045.45833333334</v>
       </c>
       <c r="B3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="C3" t="n">
-        <v>2.2</v>
-      </c>
+        <v>0.35</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>6.8</v>
+        <v>0.46</v>
       </c>
       <c r="E3" t="n">
-        <v>3.9</v>
+        <v>0.5</v>
       </c>
       <c r="F3" t="n">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
       <c r="G3" t="n">
-        <v>3.4</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>5</v>
-      </c>
-      <c r="J3" t="n">
-        <v>2</v>
-      </c>
+        <v>0.45</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>3.7</v>
+        <v>0.66</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>硫化氢(H₂S)</t>
+          <t>苯</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46126.41666666666</v>
+        <v>46045.5</v>
       </c>
       <c r="B4" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="C4" t="n">
-        <v>2</v>
-      </c>
+        <v>0.32</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>5.8</v>
+        <v>0.43</v>
       </c>
       <c r="E4" t="n">
-        <v>4.8</v>
+        <v>0.53</v>
       </c>
       <c r="F4" t="n">
-        <v>3.6</v>
+        <v>1.27</v>
       </c>
       <c r="G4" t="n">
-        <v>218.9</v>
+        <v>0.58</v>
       </c>
       <c r="H4" t="n">
-        <v>2.3</v>
+        <v>0.82</v>
       </c>
       <c r="I4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2</v>
-      </c>
+        <v>0.47</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>硫化氢(H₂S)</t>
+          <t>苯</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46126.45833333334</v>
+        <v>46045.54166666666</v>
       </c>
       <c r="B5" t="n">
-        <v>3.6</v>
+        <v>0.27</v>
       </c>
       <c r="C5" t="n">
-        <v>2.5</v>
+        <v>678.6900000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>6.6</v>
+        <v>0.4</v>
       </c>
       <c r="E5" t="n">
-        <v>5.9</v>
+        <v>0.43</v>
       </c>
       <c r="F5" t="n">
-        <v>3.3</v>
+        <v>1.16</v>
       </c>
       <c r="G5" t="n">
-        <v>7.6</v>
+        <v>0.63</v>
       </c>
       <c r="H5" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="I5" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2.2</v>
-      </c>
+        <v>0.43</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>4.3</v>
+        <v>0.89</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>硫化氢(H₂S)</t>
+          <t>苯</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46126.5</v>
+        <v>46045.58333333334</v>
       </c>
       <c r="B6" t="n">
-        <v>3.7</v>
+        <v>0.22</v>
       </c>
       <c r="C6" t="n">
-        <v>1.6</v>
+        <v>614.35</v>
       </c>
       <c r="D6" t="n">
-        <v>6.9</v>
+        <v>0.34</v>
       </c>
       <c r="E6" t="n">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="F6" t="n">
-        <v>3.5</v>
+        <v>1.48</v>
       </c>
       <c r="G6" t="n">
-        <v>4.6</v>
+        <v>0.48</v>
       </c>
       <c r="H6" t="n">
-        <v>2.3</v>
+        <v>1.13</v>
       </c>
       <c r="I6" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2.2</v>
-      </c>
+        <v>0.42</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>4.3</v>
+        <v>0.62</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>硫化氢(H₂S)</t>
+          <t>苯</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46126.54166666666</v>
+        <v>46045.625</v>
       </c>
       <c r="B7" t="n">
-        <v>3.7</v>
+        <v>0.36</v>
       </c>
       <c r="C7" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>6.3</v>
+        <v>0.41</v>
       </c>
       <c r="E7" t="n">
-        <v>56.5</v>
+        <v>0.48</v>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>0.66</v>
       </c>
       <c r="G7" t="n">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="H7" t="n">
-        <v>1.7</v>
+        <v>0.96</v>
       </c>
       <c r="I7" t="n">
-        <v>5</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2</v>
-      </c>
+        <v>0.44</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
-        <v>4.2</v>
+        <v>0.08</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>硫化氢(H₂S)</t>
+          <t>苯</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46126.58333333334</v>
+        <v>46045.66666666666</v>
       </c>
       <c r="B8" t="n">
-        <v>3.5</v>
+        <v>0.39</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>848.1</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>0.48</v>
       </c>
       <c r="E8" t="n">
-        <v>247</v>
+        <v>0.97</v>
       </c>
       <c r="F8" t="n">
-        <v>2.9</v>
+        <v>1.66</v>
       </c>
       <c r="G8" t="n">
-        <v>3.3</v>
+        <v>0.59</v>
       </c>
       <c r="H8" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="I8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1.6</v>
-      </c>
+        <v>0.52</v>
+      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>3.5</v>
+        <v>0.08</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>硫化氢(H₂S)</t>
+          <t>苯</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46126.625</v>
+        <v>46045.70833333334</v>
       </c>
       <c r="B9" t="n">
-        <v>4.4</v>
+        <v>0.46</v>
       </c>
       <c r="C9" t="n">
-        <v>1.8</v>
+        <v>835.26</v>
       </c>
       <c r="D9" t="n">
-        <v>6.1</v>
+        <v>0.53</v>
       </c>
       <c r="E9" t="n">
-        <v>7.4</v>
+        <v>0.8</v>
       </c>
       <c r="F9" t="n">
-        <v>3.2</v>
+        <v>3.78</v>
       </c>
       <c r="G9" t="n">
-        <v>3.5</v>
+        <v>0.83</v>
       </c>
       <c r="H9" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="I9" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2.1</v>
-      </c>
+        <v>0.71</v>
+      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
-        <v>4</v>
+        <v>0.04</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>硫化氢(H₂S)</t>
+          <t>苯</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46126.66666666666</v>
+        <v>46045.75</v>
       </c>
       <c r="B10" t="n">
-        <v>3.8</v>
+        <v>0.47</v>
       </c>
       <c r="C10" t="n">
-        <v>1.6</v>
+        <v>1111.98</v>
       </c>
       <c r="D10" t="n">
-        <v>6.4</v>
+        <v>0.68</v>
       </c>
       <c r="E10" t="n">
-        <v>3.8</v>
+        <v>1.15</v>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>6.45</v>
       </c>
       <c r="G10" t="n">
-        <v>3.1</v>
+        <v>0.65</v>
       </c>
       <c r="H10" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="I10" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1.9</v>
-      </c>
+        <v>0.91</v>
+      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>3.7</v>
+        <v>0.06</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>硫化氢(H₂S)</t>
+          <t>苯</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46126.70833333334</v>
+        <v>46045.79166666666</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>0.41</v>
       </c>
       <c r="C11" t="n">
-        <v>2.4</v>
+        <v>1243.46</v>
       </c>
       <c r="D11" t="n">
-        <v>6.3</v>
+        <v>0.65</v>
       </c>
       <c r="E11" t="n">
-        <v>8.699999999999999</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>3.7</v>
+        <v>2.15</v>
       </c>
       <c r="G11" t="n">
-        <v>3.4</v>
+        <v>0.79</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>1.44</v>
       </c>
       <c r="I11" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="J11" t="n">
-        <v>2.1</v>
-      </c>
+        <v>0.63</v>
+      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
-        <v>4.3</v>
+        <v>0.08</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>硫化氢(H₂S)</t>
+          <t>苯</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46126.75</v>
+        <v>46045.83333333334</v>
       </c>
       <c r="B12" t="n">
-        <v>4.3</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="C12" t="n">
-        <v>2.6</v>
+        <v>1834.45</v>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>0.96</v>
       </c>
       <c r="E12" t="n">
-        <v>5.2</v>
+        <v>0.77</v>
       </c>
       <c r="F12" t="n">
-        <v>3.6</v>
+        <v>0.89</v>
       </c>
       <c r="G12" t="n">
-        <v>3.9</v>
+        <v>0.64</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>1.26</v>
       </c>
       <c r="I12" t="n">
-        <v>5</v>
-      </c>
-      <c r="J12" t="n">
-        <v>2.5</v>
-      </c>
+        <v>0.66</v>
+      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="n">
-        <v>4</v>
+        <v>0.06</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>硫化氢(H₂S)</t>
+          <t>苯</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46126.79166666666</v>
+        <v>46045.875</v>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
+        <v>0.63</v>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>1154.14</v>
       </c>
       <c r="D13" t="n">
-        <v>7.5</v>
+        <v>0.85</v>
       </c>
       <c r="E13" t="n">
-        <v>3.9</v>
+        <v>0.76</v>
       </c>
       <c r="F13" t="n">
-        <v>4</v>
+        <v>0.82</v>
       </c>
       <c r="G13" t="n">
-        <v>3.9</v>
+        <v>0.75</v>
       </c>
       <c r="H13" t="n">
-        <v>2.5</v>
+        <v>1.14</v>
       </c>
       <c r="I13" t="n">
-        <v>5</v>
-      </c>
-      <c r="J13" t="n">
-        <v>2.9</v>
-      </c>
+        <v>0.64</v>
+      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="n">
-        <v>4.1</v>
+        <v>0.04</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>硫化氢(H₂S)</t>
+          <t>苯</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46126.83333333334</v>
+        <v>46045.91666666666</v>
       </c>
       <c r="B14" t="n">
-        <v>3.8</v>
+        <v>0.7</v>
       </c>
       <c r="C14" t="n">
-        <v>2.1</v>
+        <v>875.9299999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>7.1</v>
+        <v>0.86</v>
       </c>
       <c r="E14" t="n">
-        <v>3.2</v>
+        <v>1.16</v>
       </c>
       <c r="F14" t="n">
-        <v>3.5</v>
+        <v>0.82</v>
       </c>
       <c r="G14" t="n">
-        <v>3.7</v>
+        <v>0.74</v>
       </c>
       <c r="H14" t="n">
-        <v>1.9</v>
+        <v>1.28</v>
       </c>
       <c r="I14" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2.7</v>
-      </c>
+        <v>0.67</v>
+      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="n">
-        <v>4.8</v>
+        <v>0.8</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>硫化氢(H₂S)</t>
+          <t>苯</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>46045.95833333334</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="C15" t="n">
+        <v>674.28</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>苯</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>46046</v>
+      </c>
+      <c r="B16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C16" t="n">
+        <v>679.13</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>苯</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>46046.04166666666</v>
+      </c>
+      <c r="B17" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C17" t="n">
+        <v>608.1900000000001</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>苯</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>46046.08333333334</v>
+      </c>
+      <c r="B18" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="C18" t="n">
+        <v>631.1900000000001</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>苯</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>46046.125</v>
+      </c>
+      <c r="B19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C19" t="n">
+        <v>700.24</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>苯</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>46046.16666666666</v>
+      </c>
+      <c r="B20" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="C20" t="n">
+        <v>791.21</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>苯</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>46046.20833333334</v>
+      </c>
+      <c r="B21" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="C21" t="n">
+        <v>911.0700000000001</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>苯</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>46046.25</v>
+      </c>
+      <c r="B22" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="C22" t="n">
+        <v>916</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>苯</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>46046.29166666666</v>
+      </c>
+      <c r="B23" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="C23" t="n">
+        <v>913.78</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>苯</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>46046.33333333334</v>
+      </c>
+      <c r="B24" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="C24" t="n">
+        <v>794.13</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>苯</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>46046.375</v>
+      </c>
+      <c r="B25" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="C25" t="n">
+        <v>837.1799999999999</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>苯</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>46046.41666666666</v>
+      </c>
+      <c r="B26" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C26" t="n">
+        <v>755.11</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>苯</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>46046.45833333334</v>
+      </c>
+      <c r="B27" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="C27" t="n">
+        <v>780.75</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>苯</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>46046.5</v>
+      </c>
+      <c r="B28" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C28" t="n">
+        <v>702.79</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>苯</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>46046.54166666666</v>
+      </c>
+      <c r="B29" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="C29" t="n">
+        <v>640.54</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>苯</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>46046.58333333334</v>
+      </c>
+      <c r="B30" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>苯</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>46046.625</v>
+      </c>
+      <c r="B31" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>苯</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>46046.66666666666</v>
+      </c>
+      <c r="B32" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>苯</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>46046.70833333334</v>
+      </c>
+      <c r="B33" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>苯</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>46046.75</v>
+      </c>
+      <c r="B34" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>苯</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>46046.79166666666</v>
+      </c>
+      <c r="B35" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>苯</t>
         </is>
       </c>
     </row>

--- a/data/shsh_js/concentration.xlsx
+++ b/data/shsh_js/concentration.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,22 +453,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>二工区东北园区站(亚南)</t>
+          <t>碳谷绿湾南部园区站（抚佳）</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>二工区南部园区站（抚佳）</t>
+          <t>碳谷绿湾东北园区站 (亚南)</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>二工区边界新联站</t>
+          <t>碳谷绿湾边界新联站</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>二工区边界国贸站</t>
+          <t>碳谷绿湾边界国贸站</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -484,521 +484,533 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46121.29166666666</v>
+        <v>46186</v>
       </c>
       <c r="B2" t="n">
-        <v>7.6</v>
+        <v>26</v>
       </c>
       <c r="C2" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>2.91</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>3.9</v>
+        <v>19.05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.5</v>
+        <v>2.11</v>
       </c>
       <c r="I2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1.8</v>
-      </c>
+        <v>5.57</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>3.9</v>
+        <v>0.9</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>硫化氢(H₂S)</t>
+          <t>乙烯</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46121.33333333334</v>
+        <v>46186.04166666666</v>
       </c>
       <c r="B3" t="n">
-        <v>7.7</v>
+        <v>59.86</v>
       </c>
       <c r="C3" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>6.9</v>
+        <v>2.12</v>
       </c>
       <c r="E3" t="n">
-        <v>3.7</v>
+        <v>0.24</v>
       </c>
       <c r="F3" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>3.8</v>
+        <v>11.15</v>
       </c>
       <c r="H3" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="I3" t="n">
-        <v>9</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1.9</v>
-      </c>
+        <v>4.89</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>0.78</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>硫化氢(H₂S)</t>
+          <t>乙烯</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46121.375</v>
+        <v>46186.08333333334</v>
       </c>
       <c r="B4" t="n">
-        <v>7.9</v>
+        <v>208.94</v>
       </c>
       <c r="C4" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>6.5</v>
+        <v>1.66</v>
       </c>
       <c r="E4" t="n">
-        <v>2.6</v>
+        <v>0.32</v>
       </c>
       <c r="F4" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>5.3</v>
+        <v>2.86</v>
       </c>
       <c r="H4" t="n">
-        <v>3.4</v>
+        <v>1.93</v>
       </c>
       <c r="I4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2.9</v>
-      </c>
+        <v>3.32</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>4.3</v>
+        <v>0.6</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>硫化氢(H₂S)</t>
+          <t>乙烯</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46121.41666666666</v>
+        <v>46186.125</v>
       </c>
       <c r="B5" t="n">
-        <v>9</v>
+        <v>159.72</v>
       </c>
       <c r="C5" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>6.8</v>
+        <v>2.11</v>
       </c>
       <c r="E5" t="n">
-        <v>12.5</v>
+        <v>0.48</v>
       </c>
       <c r="F5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>5.2</v>
+        <v>13.61</v>
       </c>
       <c r="H5" t="n">
-        <v>2.9</v>
+        <v>1.07</v>
       </c>
       <c r="I5" t="n">
-        <v>7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>4.1</v>
-      </c>
+        <v>2.78</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>7.4</v>
+        <v>0.57</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>硫化氢(H₂S)</t>
+          <t>乙烯</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46121.45833333334</v>
+        <v>46186.16666666666</v>
       </c>
       <c r="B6" t="n">
-        <v>8.699999999999999</v>
+        <v>285.62</v>
       </c>
       <c r="C6" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>7.7</v>
+        <v>1.81</v>
       </c>
       <c r="E6" t="n">
-        <v>12.6</v>
+        <v>0.06</v>
       </c>
       <c r="F6" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>4.7</v>
+        <v>0.74</v>
       </c>
       <c r="H6" t="n">
-        <v>2.8</v>
+        <v>0.97</v>
       </c>
       <c r="I6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="J6" t="n">
-        <v>4.1</v>
-      </c>
+        <v>2.12</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>5.7</v>
+        <v>0.59</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>硫化氢(H₂S)</t>
+          <t>乙烯</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46121.5</v>
+        <v>46186.20833333334</v>
       </c>
       <c r="B7" t="n">
-        <v>8.5</v>
+        <v>84.68000000000001</v>
       </c>
       <c r="C7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>6.2</v>
+        <v>1.77</v>
       </c>
       <c r="E7" t="n">
-        <v>4.5</v>
+        <v>0.88</v>
       </c>
       <c r="F7" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>3.9</v>
+        <v>0.84</v>
       </c>
       <c r="H7" t="n">
-        <v>2.5</v>
+        <v>0.78</v>
       </c>
       <c r="I7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2.3</v>
-      </c>
+        <v>2.01</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
-        <v>4.4</v>
+        <v>0.7</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>硫化氢(H₂S)</t>
+          <t>乙烯</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46121.54166666666</v>
+        <v>46186.25</v>
       </c>
       <c r="B8" t="n">
-        <v>8.1</v>
+        <v>382.92</v>
       </c>
       <c r="C8" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>243.4</v>
+        <v>1.98</v>
       </c>
       <c r="E8" t="n">
-        <v>18.9</v>
+        <v>0.05</v>
       </c>
       <c r="F8" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>4.2</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>2.8</v>
+        <v>0.96</v>
       </c>
       <c r="I8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3.5</v>
-      </c>
+        <v>1.57</v>
+      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>5.5</v>
+        <v>0.74</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>硫化氢(H₂S)</t>
+          <t>乙烯</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46121.58333333334</v>
+        <v>46186.29166666666</v>
       </c>
       <c r="B9" t="n">
-        <v>8.9</v>
+        <v>237.6</v>
       </c>
       <c r="C9" t="n">
-        <v>4.5</v>
+        <v>0.88</v>
       </c>
       <c r="D9" t="n">
-        <v>14.9</v>
+        <v>2.67</v>
       </c>
       <c r="E9" t="n">
-        <v>10.7</v>
+        <v>16.02</v>
       </c>
       <c r="F9" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>4.5</v>
+        <v>0.96</v>
       </c>
       <c r="H9" t="n">
-        <v>2.6</v>
+        <v>0.92</v>
       </c>
       <c r="I9" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3.4</v>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
-        <v>6.3</v>
+        <v>0.71</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>硫化氢(H₂S)</t>
+          <t>乙烯</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46121.625</v>
+        <v>46186.33333333334</v>
       </c>
       <c r="B10" t="n">
-        <v>10.9</v>
+        <v>154.3</v>
       </c>
       <c r="C10" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>11.6</v>
+        <v>4.18</v>
       </c>
       <c r="E10" t="n">
-        <v>18.4</v>
+        <v>2.76</v>
       </c>
       <c r="F10" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>5.8</v>
+        <v>2.04</v>
       </c>
       <c r="H10" t="n">
-        <v>3.3</v>
+        <v>0.48</v>
       </c>
       <c r="I10" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="J10" t="n">
-        <v>4.5</v>
-      </c>
+        <v>1.6</v>
+      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>7.2</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>硫化氢(H₂S)</t>
+          <t>乙烯</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46121.66666666666</v>
+        <v>46186.375</v>
       </c>
       <c r="B11" t="n">
-        <v>89.7</v>
+        <v>29.75</v>
       </c>
       <c r="C11" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>8.6</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>11.3</v>
+        <v>0.35</v>
       </c>
       <c r="F11" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>5.6</v>
+        <v>1.06</v>
       </c>
       <c r="H11" t="n">
-        <v>2.8</v>
+        <v>0.66</v>
       </c>
       <c r="I11" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3.8</v>
-      </c>
+        <v>1.54</v>
+      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
-        <v>7.3</v>
+        <v>0.79</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>硫化氢(H₂S)</t>
+          <t>乙烯</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46121.70833333334</v>
+        <v>46186.41666666666</v>
       </c>
       <c r="B12" t="n">
-        <v>133.3</v>
+        <v>1.52</v>
       </c>
       <c r="C12" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>8.9</v>
+        <v>2.49</v>
       </c>
       <c r="E12" t="n">
-        <v>6.1</v>
+        <v>0.41</v>
       </c>
       <c r="F12" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>5.3</v>
+        <v>13.14</v>
       </c>
       <c r="H12" t="n">
-        <v>3.4</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="J12" t="n">
-        <v>4.2</v>
-      </c>
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="n">
-        <v>6.8</v>
+        <v>0.52</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>硫化氢(H₂S)</t>
+          <t>乙烯</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46121.75</v>
+        <v>46186.45833333334</v>
       </c>
       <c r="B13" t="n">
-        <v>7.4</v>
+        <v>3.62</v>
       </c>
       <c r="C13" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>9.6</v>
+        <v>2.64</v>
       </c>
       <c r="E13" t="n">
-        <v>6.2</v>
+        <v>0.62</v>
       </c>
       <c r="F13" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>4.8</v>
+        <v>9.98</v>
       </c>
       <c r="H13" t="n">
-        <v>2.7</v>
+        <v>6.56</v>
       </c>
       <c r="I13" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3.2</v>
-      </c>
+        <v>1.35</v>
+      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="n">
-        <v>4.8</v>
+        <v>0.61</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>硫化氢(H₂S)</t>
+          <t>乙烯</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46121.79166666666</v>
+        <v>46186.5</v>
       </c>
       <c r="B14" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>9.699999999999999</v>
+        <v>8.34</v>
       </c>
       <c r="E14" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>5.6</v>
+        <v>15.38</v>
       </c>
       <c r="H14" t="n">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="I14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J14" t="n">
-        <v>4</v>
-      </c>
+        <v>1.09</v>
+      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="n">
-        <v>8.1</v>
+        <v>0.55</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>硫化氢(H₂S)</t>
+          <t>乙烯</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>46186.54166666666</v>
+      </c>
+      <c r="B15" t="n">
+        <v>151.35</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>7.93</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>乙烯</t>
         </is>
       </c>
     </row>

--- a/data/shsh_js/concentration.xlsx
+++ b/data/shsh_js/concentration.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,35 +484,35 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46186</v>
+        <v>46212.08333333334</v>
       </c>
       <c r="B2" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>62.21</v>
       </c>
       <c r="D2" t="n">
-        <v>2.91</v>
+        <v>425.27</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>6.77</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>19.05</v>
+        <v>6</v>
       </c>
       <c r="H2" t="n">
-        <v>2.11</v>
+        <v>28.88</v>
       </c>
       <c r="I2" t="n">
-        <v>5.57</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>0.9</v>
+        <v>0.26</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -522,35 +522,33 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46186.04166666666</v>
+        <v>46212.125</v>
       </c>
       <c r="B3" t="n">
-        <v>59.86</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>134.42</v>
       </c>
       <c r="D3" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.24</v>
-      </c>
+        <v>148.64</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>11.15</v>
+        <v>4.06</v>
       </c>
       <c r="H3" t="n">
-        <v>1.48</v>
+        <v>52.84</v>
       </c>
       <c r="I3" t="n">
-        <v>4.89</v>
+        <v>9.15</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>0.78</v>
+        <v>0.44</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -560,35 +558,35 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46186.08333333334</v>
+        <v>46212.16666666666</v>
       </c>
       <c r="B4" t="n">
-        <v>208.94</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>28.77</v>
       </c>
       <c r="D4" t="n">
-        <v>1.66</v>
+        <v>61.75</v>
       </c>
       <c r="E4" t="n">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>2.86</v>
+        <v>1.75</v>
       </c>
       <c r="H4" t="n">
-        <v>1.93</v>
+        <v>5.64</v>
       </c>
       <c r="I4" t="n">
-        <v>3.32</v>
+        <v>10.08</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>0.6</v>
+        <v>0.98</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -598,35 +596,35 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46186.125</v>
+        <v>46212.20833333334</v>
       </c>
       <c r="B5" t="n">
-        <v>159.72</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="D5" t="n">
-        <v>2.11</v>
+        <v>118</v>
       </c>
       <c r="E5" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>0.99</v>
       </c>
       <c r="G5" t="n">
-        <v>13.61</v>
+        <v>0.71</v>
       </c>
       <c r="H5" t="n">
-        <v>1.07</v>
+        <v>2.26</v>
       </c>
       <c r="I5" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>0.57</v>
+        <v>0.73</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -636,35 +634,35 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46186.16666666666</v>
+        <v>46212.25</v>
       </c>
       <c r="B6" t="n">
-        <v>285.62</v>
+        <v>15.16</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="D6" t="n">
-        <v>1.81</v>
+        <v>173.32</v>
       </c>
       <c r="E6" t="n">
-        <v>0.06</v>
+        <v>20.75</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>35.99</v>
       </c>
       <c r="G6" t="n">
-        <v>0.74</v>
+        <v>7.52</v>
       </c>
       <c r="H6" t="n">
-        <v>0.97</v>
+        <v>2.94</v>
       </c>
       <c r="I6" t="n">
-        <v>2.12</v>
+        <v>0.21</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>0.59</v>
+        <v>3.1</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -674,35 +672,35 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46186.20833333334</v>
+        <v>46212.29166666666</v>
       </c>
       <c r="B7" t="n">
-        <v>84.68000000000001</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>1.77</v>
+        <v>164.25</v>
       </c>
       <c r="E7" t="n">
-        <v>0.88</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="G7" t="n">
-        <v>0.84</v>
+        <v>9.18</v>
       </c>
       <c r="H7" t="n">
-        <v>0.78</v>
+        <v>5.45</v>
       </c>
       <c r="I7" t="n">
-        <v>2.01</v>
+        <v>0.65</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
-        <v>0.7</v>
+        <v>48.33</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -712,35 +710,35 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46186.25</v>
+        <v>46212.33333333334</v>
       </c>
       <c r="B8" t="n">
-        <v>382.92</v>
+        <v>0.58</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>1.98</v>
+        <v>254.48</v>
       </c>
       <c r="E8" t="n">
-        <v>0.05</v>
+        <v>1.28</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>50.66</v>
       </c>
       <c r="H8" t="n">
-        <v>0.96</v>
+        <v>1.42</v>
       </c>
       <c r="I8" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>0.74</v>
+        <v>13.31</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -750,35 +748,35 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46186.29166666666</v>
+        <v>46212.375</v>
       </c>
       <c r="B9" t="n">
-        <v>237.6</v>
+        <v>0.49</v>
       </c>
       <c r="C9" t="n">
-        <v>0.88</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>2.67</v>
+        <v>62.48</v>
       </c>
       <c r="E9" t="n">
-        <v>16.02</v>
+        <v>3.62</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>35.4</v>
       </c>
       <c r="G9" t="n">
-        <v>0.96</v>
+        <v>18.24</v>
       </c>
       <c r="H9" t="n">
-        <v>0.92</v>
+        <v>1.29</v>
       </c>
       <c r="I9" t="n">
-        <v>0.95</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
-        <v>0.71</v>
+        <v>0.78</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -788,35 +786,35 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46186.33333333334</v>
+        <v>46212.41666666666</v>
       </c>
       <c r="B10" t="n">
-        <v>154.3</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>10.61</v>
       </c>
       <c r="D10" t="n">
-        <v>4.18</v>
+        <v>48.14</v>
       </c>
       <c r="E10" t="n">
-        <v>2.76</v>
+        <v>3.91</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="G10" t="n">
-        <v>2.04</v>
+        <v>0.92</v>
       </c>
       <c r="H10" t="n">
-        <v>0.48</v>
+        <v>0.04</v>
       </c>
       <c r="I10" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.78</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -826,35 +824,35 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46186.375</v>
+        <v>46212.45833333334</v>
       </c>
       <c r="B11" t="n">
-        <v>29.75</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>10.52</v>
       </c>
       <c r="D11" t="n">
-        <v>9.710000000000001</v>
+        <v>94.58</v>
       </c>
       <c r="E11" t="n">
-        <v>0.35</v>
+        <v>5.13</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>1.06</v>
+        <v>0.44</v>
       </c>
       <c r="H11" t="n">
-        <v>0.66</v>
+        <v>0.04</v>
       </c>
       <c r="I11" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
-        <v>0.79</v>
+        <v>0.38</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -864,35 +862,35 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46186.41666666666</v>
+        <v>46212.5</v>
       </c>
       <c r="B12" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>10.56</v>
       </c>
       <c r="D12" t="n">
-        <v>2.49</v>
+        <v>46.55</v>
       </c>
       <c r="E12" t="n">
-        <v>0.41</v>
+        <v>10.57</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>68.54000000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>13.14</v>
+        <v>1.2</v>
       </c>
       <c r="H12" t="n">
-        <v>9.789999999999999</v>
+        <v>0.09</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.37</v>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="n">
-        <v>0.52</v>
+        <v>1.53</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -902,35 +900,35 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46186.45833333334</v>
+        <v>46212.54166666666</v>
       </c>
       <c r="B13" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>2.64</v>
+        <v>63.75</v>
       </c>
       <c r="E13" t="n">
-        <v>0.62</v>
+        <v>4.64</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>30.21</v>
       </c>
       <c r="G13" t="n">
-        <v>9.98</v>
+        <v>2.79</v>
       </c>
       <c r="H13" t="n">
-        <v>6.56</v>
+        <v>0.06</v>
       </c>
       <c r="I13" t="n">
-        <v>1.35</v>
+        <v>0.49</v>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="n">
-        <v>0.61</v>
+        <v>1.58</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -940,75 +938,37 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46186.5</v>
+        <v>46212.58333333334</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.54</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>8.34</v>
+        <v>87.81999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>43.88</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>15.38</v>
+        <v>2.07</v>
       </c>
       <c r="H14" t="n">
-        <v>2.5</v>
+        <v>3.03</v>
       </c>
       <c r="I14" t="n">
-        <v>1.09</v>
+        <v>5.37</v>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="n">
-        <v>0.55</v>
+        <v>49.41</v>
       </c>
       <c r="L14" t="inlineStr">
-        <is>
-          <t>乙烯</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>46186.54166666666</v>
-      </c>
-      <c r="B15" t="n">
-        <v>151.35</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>7.93</v>
-      </c>
-      <c r="H15" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="L15" t="inlineStr">
         <is>
           <t>乙烯</t>
         </is>
